--- a/GESTION DE COMPOSTAJE.xlsx
+++ b/GESTION DE COMPOSTAJE.xlsx
@@ -8,20 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://angloamerican-my.sharepoint.com/personal/mishel_ruiz_angloamerican_com/Documents/Documents/MISHEL_PRACTICAS 2026_ANGLO/DASHBOARD DE COMPOST/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{251E0871-5502-4621-B0CF-4266A8053F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="445" documentId="8_{251E0871-5502-4621-B0CF-4266A8053F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15FEE4B1-513C-406D-837C-BC18871A9831}"/>
   <bookViews>
-    <workbookView xWindow="2240" yWindow="2240" windowWidth="14400" windowHeight="7270" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="HOJA 1. CONFIGURACION" sheetId="11" r:id="rId1"/>
-    <sheet name="HOJA 2. INSUMOS" sheetId="10" r:id="rId2"/>
-    <sheet name="HOJA 3. FORMULACION" sheetId="15" r:id="rId3"/>
-    <sheet name="bloque auxiliar" sheetId="16" r:id="rId4"/>
-    <sheet name="Calculo progresivo por lote" sheetId="17" r:id="rId5"/>
-    <sheet name="HOJA 4-SEGUIMIENTO" sheetId="8" r:id="rId6"/>
-    <sheet name="HOJA 5. INVENTARIO (STOCK)" sheetId="9" r:id="rId7"/>
-    <sheet name="HOJA 6. INDICADORES" sheetId="12" r:id="rId8"/>
-    <sheet name="BASE_CONOCIMIENTOS " sheetId="13" r:id="rId9"/>
+    <sheet name="HOJA 2. INSUMOS" sheetId="10" r:id="rId1"/>
+    <sheet name="HOJA 3. FORMULACION" sheetId="15" r:id="rId2"/>
+    <sheet name="bloque auxiliar" sheetId="16" r:id="rId3"/>
+    <sheet name="Calculo progresivo por lote" sheetId="17" r:id="rId4"/>
+    <sheet name="HOJA 4-SEGUIMIENTO" sheetId="8" r:id="rId5"/>
+    <sheet name="HOJA 5. INVENTARIO (STOCK)" sheetId="9" r:id="rId6"/>
+    <sheet name="HOJA 6. INDICADORES" sheetId="12" r:id="rId7"/>
+    <sheet name="HOJA 7. CAPACIDAD DE LODO" sheetId="18" r:id="rId8"/>
+    <sheet name="HOJA 1. CONFIGURACION" sheetId="11" r:id="rId9"/>
+    <sheet name="BASE_CONOCIMIENTOS " sheetId="13" r:id="rId10"/>
+    <sheet name="VALIDACION DEL SISTEMA" sheetId="19" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -75,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="279">
   <si>
     <t xml:space="preserve">Residuos organicos </t>
   </si>
@@ -723,6 +725,195 @@
   </si>
   <si>
     <t>EN ALIMENTACION</t>
+  </si>
+  <si>
+    <t>Residuos Organicos disponibles (ton)</t>
+  </si>
+  <si>
+    <t>Residuos organicos deshidratados disponibles (ton)</t>
+  </si>
+  <si>
+    <t>Carton/material estructurante disponible (ton)</t>
+  </si>
+  <si>
+    <t>Carbono total de los materiales sin lodo (ton)</t>
+  </si>
+  <si>
+    <t>Nitrogeno total de los materiales sin lodo (ton)</t>
+  </si>
+  <si>
+    <t>Carbono aportado por 1 tonelada de lodo (Ton C/Ton lodo)</t>
+  </si>
+  <si>
+    <t>Nitrogeno aportado por 1 tonelada de lodo (Ton N/Ton lodo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lodo Maximo por C/N </t>
+  </si>
+  <si>
+    <t>Agua total de materiales sin lodo (ton)</t>
+  </si>
+  <si>
+    <t>Masa total sin lodo</t>
+  </si>
+  <si>
+    <t>Lodo maximo por humedad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se representa la humedad inicial de la pila, no la humedad final del compost terminado </t>
+  </si>
+  <si>
+    <t>lodo recomendado (ton)</t>
+  </si>
+  <si>
+    <t>masa total de formulacion (ton)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">humedad resultante de la formulacion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relacion C/N Resultante </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estado del simulador </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recomendación </t>
+  </si>
+  <si>
+    <t>Capacidad de lodo</t>
+  </si>
+  <si>
+    <t>R-016</t>
+  </si>
+  <si>
+    <t>R-017</t>
+  </si>
+  <si>
+    <t>R-018</t>
+  </si>
+  <si>
+    <t>La cantidad de lodo propuesta cumple el criterio de relación C/N para la formulación inicial.</t>
+  </si>
+  <si>
+    <t>C/N resultante ≥ límite mínimo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estado de capacidad </t>
+  </si>
+  <si>
+    <t>C/N cumple, pero humedad resultante &lt; límite mínimo</t>
+  </si>
+  <si>
+    <t>Ajustar humedad</t>
+  </si>
+  <si>
+    <t>La cantidad de lodo es admisible por C/N, pero se requiere incrementar la humedad de la mezcla antes de conformar la pila</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	C/N resultante &lt; límite mínimo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La cantidad de lodo propuesta no cumple los criterios establecidos. Ajustar la cantidad de lodo y/o la composicion de la mezcla antes de conformar la pila. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADMISIBLE </t>
+  </si>
+  <si>
+    <t>ADMISIBLE CON AJUSTE DE HUMEDAD</t>
+  </si>
+  <si>
+    <t>NO ADMISIBLE</t>
+  </si>
+  <si>
+    <t>C/N maxima permitida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C/N minima permitida </t>
+  </si>
+  <si>
+    <t>Humedad Maxima permitida (%)</t>
+  </si>
+  <si>
+    <t>Humedad minima permitida (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entradas principales </t>
+  </si>
+  <si>
+    <t>Caso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resultado esperado </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resultado obtenido </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estado esperado </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estado obtenido </t>
+  </si>
+  <si>
+    <t>¿Cumple?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observacion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumple ambos criterios </t>
+  </si>
+  <si>
+    <t>R0 8T, ROD 0T, Carton 3T</t>
+  </si>
+  <si>
+    <t>RO 10T, ROD 4T, Carton 5T</t>
+  </si>
+  <si>
+    <t>RO 2T, ROD 0T, Carton 0T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C/N dentro de rango y humedad dentro de rango </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C/N cumple, humedad baja </t>
+  </si>
+  <si>
+    <t xml:space="preserve">No debe admitir lodo </t>
+  </si>
+  <si>
+    <t>C/n = 25, Humedad =55%</t>
+  </si>
+  <si>
+    <t>C/n = 25, Humedad =45%</t>
+  </si>
+  <si>
+    <t>Lodo recomendado 0T, C/N =15, humedad = 80%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO ADMISIBLE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADMISIBLE CON AJUSTE DE HUMEDAD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADMISIBLE  </t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requiere ajustes de humedad </t>
+  </si>
+  <si>
+    <t>Mezcla inicial no apta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recomendación esperada </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recomendación obtenida </t>
   </si>
 </sst>
 </file>
@@ -733,7 +924,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
@@ -862,8 +1053,38 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -918,8 +1139,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -980,11 +1231,118 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1146,14 +1504,41 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1165,12 +1550,91 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="11" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="22" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1235,9 +1699,6 @@
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1557,6 +2018,60 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1810,63 +2325,12 @@
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF9999"/>
       <color rgb="FFCC0066"/>
-      <color rgb="FFFF9999"/>
       <color rgb="FFFFCC66"/>
     </mruColors>
   </colors>
@@ -1882,72 +2346,56 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{DC0FC455-24CF-4E66-B8C2-52D6A3F8C0AC}" name="Table9" displayName="Table9" ref="A2:G11" totalsRowShown="0" dataDxfId="81">
-  <autoFilter ref="A2:G11" xr:uid="{DC0FC455-24CF-4E66-B8C2-52D6A3F8C0AC}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{CC3B574F-E27F-413D-97E8-9537DF94269A}" name="Parametro"/>
-    <tableColumn id="7" xr3:uid="{31105658-6F32-48B6-8876-D035B990630C}" name="Unidad" dataDxfId="80"/>
-    <tableColumn id="2" xr3:uid="{D682FB6B-9E90-457D-96A4-807678C3D581}" name="Mesófila I" dataDxfId="79"/>
-    <tableColumn id="3" xr3:uid="{FEA1E499-9B43-4E54-A972-9209C66C98D9}" name="Termófila " dataDxfId="78"/>
-    <tableColumn id="4" xr3:uid="{13C8682C-BAE4-4F99-BBFD-7E52F56B6430}" name="Mesófila II" dataDxfId="77"/>
-    <tableColumn id="5" xr3:uid="{843FA08B-D107-4ADF-B5AC-FD2EEDFCE796}" name="Maduración" dataDxfId="76"/>
-    <tableColumn id="6" xr3:uid="{A288719C-2759-48F8-AB04-6B0F737C89CB}" name="Fuente: " dataDxfId="75"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3A0866CB-3DC5-481D-8C83-6B8960D40213}" name="Table3" displayName="Table3" ref="A1:H5" insertRowShift="1" totalsRowShown="0">
+  <autoFilter ref="A1:H5" xr:uid="{3A0866CB-3DC5-481D-8C83-6B8960D40213}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{632EF686-0ED9-4D03-8407-B9925D062B63}" name="Nombre de insumo"/>
+    <tableColumn id="8" xr3:uid="{EBB11E2C-64EF-4641-AFCC-82F5F73E29FF}" name="codigo de insumo "/>
+    <tableColumn id="2" xr3:uid="{7DA1F54F-D3F5-4927-A3F4-9216C09ADB8C}" name="Humedad (%)" dataDxfId="87"/>
+    <tableColumn id="3" xr3:uid="{2ECF8BD7-8192-4479-99A0-F766E5FD2C7F}" name="Carbono (%)" dataDxfId="86"/>
+    <tableColumn id="4" xr3:uid="{231E1900-6DC3-439A-BECA-1CE8FA087FD4}" name="Nitrogeno (%)" dataDxfId="85"/>
+    <tableColumn id="5" xr3:uid="{E5B09940-1D3C-4D58-89C7-0AA2FCB76389}" name="Relacion C/N" dataDxfId="84"/>
+    <tableColumn id="6" xr3:uid="{187E6D5B-F5CA-4114-B3E1-F540BE1C26E4}" name="Densidad (Kg/m3)" dataDxfId="83"/>
+    <tableColumn id="7" xr3:uid="{D0DE92C8-A852-446C-86C0-8F6CB9AF3857}" name="Fuente"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3A0866CB-3DC5-481D-8C83-6B8960D40213}" name="Table3" displayName="Table3" ref="A1:H5" insertRowShift="1" totalsRowShown="0">
-  <autoFilter ref="A1:H5" xr:uid="{3A0866CB-3DC5-481D-8C83-6B8960D40213}"/>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{632EF686-0ED9-4D03-8407-B9925D062B63}" name="Nombre de insumo"/>
-    <tableColumn id="8" xr3:uid="{EBB11E2C-64EF-4641-AFCC-82F5F73E29FF}" name="codigo de insumo "/>
-    <tableColumn id="2" xr3:uid="{7DA1F54F-D3F5-4927-A3F4-9216C09ADB8C}" name="Humedad (%)" dataDxfId="74"/>
-    <tableColumn id="3" xr3:uid="{2ECF8BD7-8192-4479-99A0-F766E5FD2C7F}" name="Carbono (%)" dataDxfId="73"/>
-    <tableColumn id="4" xr3:uid="{231E1900-6DC3-439A-BECA-1CE8FA087FD4}" name="Nitrogeno (%)" dataDxfId="72"/>
-    <tableColumn id="5" xr3:uid="{E5B09940-1D3C-4D58-89C7-0AA2FCB76389}" name="Relacion C/N" dataDxfId="71"/>
-    <tableColumn id="6" xr3:uid="{187E6D5B-F5CA-4114-B3E1-F540BE1C26E4}" name="Densidad (Kg/m3)" dataDxfId="70"/>
-    <tableColumn id="7" xr3:uid="{D0DE92C8-A852-446C-86C0-8F6CB9AF3857}" name="Fuente"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F1DAEA86-B06B-4A28-BC0E-4E6D2786F910}" name="Table211" displayName="Table211" ref="A2:W8" totalsRowShown="0" headerRowDxfId="69">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F1DAEA86-B06B-4A28-BC0E-4E6D2786F910}" name="Table211" displayName="Table211" ref="A2:W8" totalsRowShown="0" headerRowDxfId="82">
   <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{B9DE8FBA-E9BD-4669-9330-8DBE65C8FAF0}" name="FECHA" dataDxfId="68"/>
-    <tableColumn id="10" xr3:uid="{7C883F31-9D14-4CF5-B692-F36AAD7A9187}" name="OPERADOR" dataDxfId="67"/>
-    <tableColumn id="11" xr3:uid="{C6E1BB0F-B2D5-40A5-AFF4-500B97BA937D}" name="CODIGO DE LOTE" dataDxfId="66"/>
+    <tableColumn id="1" xr3:uid="{B9DE8FBA-E9BD-4669-9330-8DBE65C8FAF0}" name="FECHA" dataDxfId="81"/>
+    <tableColumn id="10" xr3:uid="{7C883F31-9D14-4CF5-B692-F36AAD7A9187}" name="OPERADOR" dataDxfId="80"/>
+    <tableColumn id="11" xr3:uid="{C6E1BB0F-B2D5-40A5-AFF4-500B97BA937D}" name="CODIGO DE LOTE" dataDxfId="79"/>
     <tableColumn id="4" xr3:uid="{27F1045F-4B29-4CC7-98B4-88AB81431037}" name="TONELADAS DE RESIDUOS ORGANICOS"/>
     <tableColumn id="9" xr3:uid="{F1211492-7E42-44D0-AA02-2CEC4FC387C1}" name="TONELADAS DE RESIDUOS ORGANICOS DESHIDRATADOS"/>
     <tableColumn id="5" xr3:uid="{104EB3C8-8B4F-40A1-BC5C-2032A3D2207C}" name="TONELADAS DE LODO "/>
     <tableColumn id="6" xr3:uid="{E726AF50-9DB4-4779-ABF0-C857E1CF5CC1}" name="TONELADAS DE CARTÓN "/>
     <tableColumn id="8" xr3:uid="{DBED4005-5759-4B93-83C5-519C1C2C5448}" name="COMENTARIOS"/>
-    <tableColumn id="17" xr3:uid="{667C3E19-FC42-44C2-8BBE-5A075F4FA64C}" name="TOTAL DIARIO" dataDxfId="65">
+    <tableColumn id="17" xr3:uid="{667C3E19-FC42-44C2-8BBE-5A075F4FA64C}" name="TOTAL DIARIO" dataDxfId="78">
       <calculatedColumnFormula>SUM(Table211[[#This Row],[TONELADAS DE RESIDUOS ORGANICOS]:[TONELADAS DE CARTÓN ]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{8C2EDE30-76EB-43A9-B242-FA233B3C0804}" name="TOTAL ACUMULADO DE LOTE " dataDxfId="64">
+    <tableColumn id="18" xr3:uid="{8C2EDE30-76EB-43A9-B242-FA233B3C0804}" name="TOTAL ACUMULADO DE LOTE " dataDxfId="77">
       <calculatedColumnFormula>SUMIFS($I$3:I3,$C$3:C3,C3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{1062FF25-76A4-4E2A-8BCB-FBFA53890464}" name="ESTADO DE LOTE " dataDxfId="63"/>
-    <tableColumn id="2" xr3:uid="{17A97C9A-D065-4C8B-8FC6-668B80DE80E1}" name="Humedad inicial de la mezcla (%)" dataDxfId="62">
+    <tableColumn id="24" xr3:uid="{1062FF25-76A4-4E2A-8BCB-FBFA53890464}" name="ESTADO DE LOTE " dataDxfId="76"/>
+    <tableColumn id="2" xr3:uid="{17A97C9A-D065-4C8B-8FC6-668B80DE80E1}" name="Humedad inicial de la mezcla (%)" dataDxfId="75">
       <calculatedColumnFormula>'Calculo progresivo por lote'!M3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{438933E1-D9AF-4710-8463-89F084161E67}" name="Carbono total en base seca (Ton o kg)" dataDxfId="61">
+    <tableColumn id="3" xr3:uid="{438933E1-D9AF-4710-8463-89F084161E67}" name="Carbono total en base seca (Ton o kg)" dataDxfId="74">
       <calculatedColumnFormula>'Calculo progresivo por lote'!N3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{86B97DBB-43F8-4DB7-9CB6-A0D3FC8C0DF9}" name="Nitrogeno total en base seca (ton o kg) " dataDxfId="60">
+    <tableColumn id="12" xr3:uid="{86B97DBB-43F8-4DB7-9CB6-A0D3FC8C0DF9}" name="Nitrogeno total en base seca (ton o kg) " dataDxfId="73">
       <calculatedColumnFormula>'Calculo progresivo por lote'!O3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{58CA3B42-5E75-4A5C-BD3B-ED83FA780087}" name="Relacion C/N  inicial " dataDxfId="59">
+    <tableColumn id="13" xr3:uid="{58CA3B42-5E75-4A5C-BD3B-ED83FA780087}" name="Relacion C/N  inicial " dataDxfId="72">
       <calculatedColumnFormula>'Calculo progresivo por lote'!O3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{0DC2F583-ADF7-49E1-BA56-4409FB13512C}" name="Masa total de la mezcla  calculada (ton)" dataDxfId="58">
+    <tableColumn id="14" xr3:uid="{0DC2F583-ADF7-49E1-BA56-4409FB13512C}" name="Masa total de la mezcla  calculada (ton)" dataDxfId="71">
       <calculatedColumnFormula>SUM(D3:G3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{F9D0CDB0-0B3B-430A-AA40-11C92BE93E66}" name="Recomendaciones del sistema " dataDxfId="57">
+    <tableColumn id="15" xr3:uid="{F9D0CDB0-0B3B-430A-AA40-11C92BE93E66}" name="Recomendaciones del sistema " dataDxfId="70">
       <calculatedColumnFormula>IF(OR(R3="",S3=""),"",
 IF(AND(R3="CORRECTA",S3="CORRECTO"),
 "La formulación cumple los criterios iniciales para conformar la pila.",
@@ -1969,26 +2417,26 @@
 "Incrementar material con mayor aporte de nitrógeno.",
 "Revisar la formulación."))))))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{CDA8686A-5094-4B4F-8C4B-03EA7A161B4F}" name="Estado de la humedad " dataDxfId="56">
+    <tableColumn id="19" xr3:uid="{CDA8686A-5094-4B4F-8C4B-03EA7A161B4F}" name="Estado de la humedad " dataDxfId="69">
       <calculatedColumnFormula>IF(L3&lt;'HOJA 1. CONFIGURACION'!$C$5,"BAJA",
 IF(L3&gt;'HOJA 1. CONFIGURACION'!$C$6,"ALTA",
 "CORRECTA"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{DB258EAA-4022-4DB2-8D0E-02B200E3487E}" name="Estado de la relacion C/N" dataDxfId="55">
+    <tableColumn id="20" xr3:uid="{DB258EAA-4022-4DB2-8D0E-02B200E3487E}" name="Estado de la relacion C/N" dataDxfId="68">
       <calculatedColumnFormula>IF(O3&lt;'HOJA 1. CONFIGURACION'!$C$9,"BAJO",
 IF(O3&gt;'HOJA 1. CONFIGURACION'!$C$10,"ALTO",
 "CORRECTO"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{6BDF3539-3022-4BA9-824F-84F855424CDA}" name="Estado de la formulación" dataDxfId="54">
+    <tableColumn id="21" xr3:uid="{6BDF3539-3022-4BA9-824F-84F855424CDA}" name="Estado de la formulación" dataDxfId="67">
       <calculatedColumnFormula>IF(OR(R3="",S3=""),"",IF(AND(TRIM(R3)="CORRECTA",TRIM(S3)="CORRECTO"),"APROBADA","REFORMULAR"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{147D7839-841E-474C-AC32-15C35F290B02}" name="Recomendación para humedad" dataDxfId="53">
+    <tableColumn id="23" xr3:uid="{147D7839-841E-474C-AC32-15C35F290B02}" name="Recomendación para humedad" dataDxfId="66">
       <calculatedColumnFormula>IF(R3="","",IF(R3="CORRECTA","",_xlfn.XLOOKUP("Humedad inicial|"&amp;TRIM(R3),Table8[[CLAVE ]],Table8[Recomendación],"REGLA NO ENCONTRADA")))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{995FB719-E19D-4E29-A9A6-1CE028CAF13B}" name="Recomendación para relacion C/N" dataDxfId="52">
+    <tableColumn id="7" xr3:uid="{995FB719-E19D-4E29-A9A6-1CE028CAF13B}" name="Recomendación para relacion C/N" dataDxfId="65">
       <calculatedColumnFormula>IF(S3="","",IF(S3="CORRECTO","",_xlfn.XLOOKUP("Relacion C/N|"&amp;TRIM(S3),Table8[[CLAVE ]],Table8[Recomendación],"REGLA NO ENCONTRADA")))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{90A5E80D-627C-46D7-9BE4-04009DFAEAA2}" name="Recomendación final " dataDxfId="51">
+    <tableColumn id="16" xr3:uid="{90A5E80D-627C-46D7-9BE4-04009DFAEAA2}" name="Recomendación final " dataDxfId="64">
       <calculatedColumnFormula>IF(T3="","",IF(T3="APROBADA","La formulación cumple los parámetros establecidos para iniciar el compostaje.",_xlfn.TEXTJOIN(" | ",TRUE,U3,V3)))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1996,21 +2444,21 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FF9811BD-62EF-49DD-8162-5AD218D0D032}" name="Table1" displayName="Table1" ref="A1:I6" totalsRowShown="0">
   <autoFilter ref="A1:I6" xr:uid="{FF9811BD-62EF-49DD-8162-5AD218D0D032}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{A1B22E68-0971-468F-BC25-D5EE98897512}" name="Insumo"/>
-    <tableColumn id="2" xr3:uid="{35D51007-EDCD-4428-A784-8444CF895330}" name="Masa humeda (ton)" dataDxfId="50" totalsRowDxfId="49">
+    <tableColumn id="2" xr3:uid="{35D51007-EDCD-4428-A784-8444CF895330}" name="Masa humeda (ton)" dataDxfId="63" totalsRowDxfId="62">
       <calculatedColumnFormula>'HOJA 3. FORMULACION'!D3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{095AF084-8F19-43ED-8A63-D2FD6693C8C7}" name="Humedad (%)" dataDxfId="48" totalsRowDxfId="47">
+    <tableColumn id="3" xr3:uid="{095AF084-8F19-43ED-8A63-D2FD6693C8C7}" name="Humedad (%)" dataDxfId="61" totalsRowDxfId="60">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,'HOJA 2. INSUMOS'!$B$2:$B$5,'HOJA 2. INSUMOS'!$C$2:$C$5)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E7895FF6-5778-4DB7-AAB2-FA3D4D0E0912}" name="Masa seca (ton)" dataDxfId="46" totalsRowDxfId="45">
+    <tableColumn id="4" xr3:uid="{E7895FF6-5778-4DB7-AAB2-FA3D4D0E0912}" name="Masa seca (ton)" dataDxfId="59" totalsRowDxfId="58">
       <calculatedColumnFormula>B2*(1-C2/100)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7257609E-92DF-48C3-862A-1FEC457ECDEF}" name="Carbono (%)" dataDxfId="44" totalsRowDxfId="43">
+    <tableColumn id="5" xr3:uid="{7257609E-92DF-48C3-862A-1FEC457ECDEF}" name="Carbono (%)" dataDxfId="57" totalsRowDxfId="56">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,'HOJA 2. INSUMOS'!$B$2:$B$5,'HOJA 2. INSUMOS'!$D$2:$D$5)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{44BD1C5B-E537-4CE8-AF36-53B038AAF3BE}" name="Carbono (ton)"/>
@@ -2022,10 +2470,10 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{7528BD82-2E07-4521-A141-711237E5A8DC}" name="Table2" displayName="Table2" ref="A2:P8" totalsRowShown="0" headerRowDxfId="95">
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{7528BD82-2E07-4521-A141-711237E5A8DC}" name="Table2" displayName="Table2" ref="A2:P8" totalsRowShown="0" headerRowDxfId="55">
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{4290F5D6-CC2B-4F52-AD25-80C0F3CC7105}" name="Fecha " dataDxfId="94">
+    <tableColumn id="1" xr3:uid="{4290F5D6-CC2B-4F52-AD25-80C0F3CC7105}" name="Fecha " dataDxfId="54">
       <calculatedColumnFormula>'HOJA 3. FORMULACION'!A3</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{AC5970E9-FEE3-4F99-A483-0589F1E21FCC}" name="Codigo de lote ">
@@ -2034,24 +2482,24 @@
     <tableColumn id="3" xr3:uid="{B0967717-FCAC-4F07-8BC5-7368A7B32B1F}" name="Masa humeda diaria (ton)">
       <calculatedColumnFormula>'HOJA 3. FORMULACION'!I3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{2306B625-1E46-449A-93E8-3B0F5EEE888A}" name="Agua diaria (ton)" dataDxfId="93">
+    <tableColumn id="4" xr3:uid="{2306B625-1E46-449A-93E8-3B0F5EEE888A}" name="Agua diaria (ton)" dataDxfId="53">
       <calculatedColumnFormula>IF(B3="","",
 'HOJA 3. FORMULACION'!D3*'HOJA 2. INSUMOS'!$C$2/100+
 'HOJA 3. FORMULACION'!E3*'HOJA 2. INSUMOS'!$C$5/100+
 'HOJA 3. FORMULACION'!F3*'HOJA 2. INSUMOS'!$C$3/100+
 'HOJA 3. FORMULACION'!G3*'HOJA 2. INSUMOS'!$C$4/100)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{4BBA6E6A-026A-4B30-8776-7EF7C8594CF1}" name="Masa seca diaria (ton)" dataDxfId="92">
+    <tableColumn id="5" xr3:uid="{4BBA6E6A-026A-4B30-8776-7EF7C8594CF1}" name="Masa seca diaria (ton)" dataDxfId="52">
       <calculatedColumnFormula>IF(B3="","",C3-D3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{DCE32C46-3055-42A3-981B-6F84B606E901}" name="Carbono diario (ton)" dataDxfId="91">
+    <tableColumn id="6" xr3:uid="{DCE32C46-3055-42A3-981B-6F84B606E901}" name="Carbono diario (ton)" dataDxfId="51">
       <calculatedColumnFormula>IF(B3="","",
 'HOJA 3. FORMULACION'!D3*(1-'HOJA 2. INSUMOS'!$C$2/100)*'HOJA 2. INSUMOS'!$D$2/100+
 'HOJA 3. FORMULACION'!E3*(1-'HOJA 2. INSUMOS'!$C$5/100)*'HOJA 2. INSUMOS'!$D$5/100+
 'HOJA 3. FORMULACION'!F3*(1-'HOJA 2. INSUMOS'!$C$3/100)*'HOJA 2. INSUMOS'!$D$3/100+
 'HOJA 3. FORMULACION'!G3*(1-'HOJA 2. INSUMOS'!$C$4/100)*'HOJA 2. INSUMOS'!$D$4/100)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{AB95AAEC-6AC2-4E57-8464-79672F94CDCD}" name="Nitrogeno diario (ton)" dataDxfId="90">
+    <tableColumn id="7" xr3:uid="{AB95AAEC-6AC2-4E57-8464-79672F94CDCD}" name="Nitrogeno diario (ton)" dataDxfId="50">
       <calculatedColumnFormula>IF(B3="","",
 'HOJA 3. FORMULACION'!D3*(1-'HOJA 2. INSUMOS'!$C$2/100)*'HOJA 2. INSUMOS'!$E$2/100+
 'HOJA 3. FORMULACION'!E3*(1-'HOJA 2. INSUMOS'!$C$5/100)*'HOJA 2. INSUMOS'!$E$5/100+
@@ -2061,28 +2509,28 @@
     <tableColumn id="8" xr3:uid="{8FEFBA98-F461-4A8B-9381-5B8F29914805}" name="Masa humeda acumulada del lote (ton)">
       <calculatedColumnFormula>IF(B3="","",SUMIFS($C$3:C3,$B$3:B3,B3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{393B5CF1-1E63-4A75-BE36-1977024E4030}" name="Agua acumulada del lote (ton)" dataDxfId="89">
+    <tableColumn id="9" xr3:uid="{393B5CF1-1E63-4A75-BE36-1977024E4030}" name="Agua acumulada del lote (ton)" dataDxfId="49">
       <calculatedColumnFormula>IF(B3="","",SUMIFS($D$3:D3,$B$3:B3,B3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{F31BEBE2-C6D7-419B-AA71-A745BAC36C55}" name="Masa seca acumulada por lote(ton)" dataDxfId="88">
+    <tableColumn id="10" xr3:uid="{F31BEBE2-C6D7-419B-AA71-A745BAC36C55}" name="Masa seca acumulada por lote(ton)" dataDxfId="48">
       <calculatedColumnFormula>IF(B3="","",SUMIFS($E$3:E3,$B$3:B3,B3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{7F562FFF-134F-4C23-B34B-C337053A771A}" name="Carbono acumulado del lote (ton)" dataDxfId="87">
+    <tableColumn id="11" xr3:uid="{7F562FFF-134F-4C23-B34B-C337053A771A}" name="Carbono acumulado del lote (ton)" dataDxfId="47">
       <calculatedColumnFormula>IF(B3="","",SUMIFS($F$3:F3,$B$3:B3,B3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{1A2AC99D-E163-4BD0-BA98-1CEFE9EA98CD}" name="Nitrogeno acumulado del lote (ton)" dataDxfId="86">
+    <tableColumn id="12" xr3:uid="{1A2AC99D-E163-4BD0-BA98-1CEFE9EA98CD}" name="Nitrogeno acumulado del lote (ton)" dataDxfId="46">
       <calculatedColumnFormula>IF(B3="","",SUMIFS($G$3:G3,$B$3:B3,B3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{271BEABA-A2C2-4C15-8251-18C17AF7DE3C}" name="Humedad acumulada (%)" dataDxfId="85">
+    <tableColumn id="13" xr3:uid="{271BEABA-A2C2-4C15-8251-18C17AF7DE3C}" name="Humedad acumulada (%)" dataDxfId="45">
       <calculatedColumnFormula>IF(H3=0,"",I3/H3*100)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{819E3F59-E70A-40D2-8257-63D2D6333059}" name="Carbono acumulado en base seca (%)" dataDxfId="84">
+    <tableColumn id="14" xr3:uid="{819E3F59-E70A-40D2-8257-63D2D6333059}" name="Carbono acumulado en base seca (%)" dataDxfId="44">
       <calculatedColumnFormula>IF(J3=0,"",K3/J3*100)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{7148EBD2-7CD6-49BB-8180-BD35A4753F5F}" name="Nitrogeno acumulado en base seca (%)" dataDxfId="83">
+    <tableColumn id="15" xr3:uid="{7148EBD2-7CD6-49BB-8180-BD35A4753F5F}" name="Nitrogeno acumulado en base seca (%)" dataDxfId="43">
       <calculatedColumnFormula>IF(J3=0,"",L3/J3*100)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{023CEFED-1DF8-41BF-BE31-BD5246633D19}" name="Relacion C/N acumulada" dataDxfId="82">
+    <tableColumn id="16" xr3:uid="{023CEFED-1DF8-41BF-BE31-BD5246633D19}" name="Relacion C/N acumulada" dataDxfId="42">
       <calculatedColumnFormula>IF(L3=0,"",K3/L3)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2090,50 +2538,50 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{1D9ED920-C41F-4D95-AD0D-5D8EE860FDE0}" name="Table4" displayName="Table4" ref="A1:T2" totalsRowShown="0" headerRowDxfId="42" headerRowBorderDxfId="41" tableBorderDxfId="40">
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{1D9ED920-C41F-4D95-AD0D-5D8EE860FDE0}" name="Table4" displayName="Table4" ref="A1:T2" totalsRowShown="0" headerRowDxfId="41" headerRowBorderDxfId="40" tableBorderDxfId="39">
   <autoFilter ref="A1:T2" xr:uid="{1D9ED920-C41F-4D95-AD0D-5D8EE860FDE0}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{F3C78A2A-E049-44AD-BCEF-3623D50497A2}" name="OPERADOR" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{A98DA936-BC9E-4B55-BBD8-F045C36ABADE}" name="Fecha  de evaluación  (dd/mm/aa)" dataDxfId="38"/>
-    <tableColumn id="6" xr3:uid="{71676037-992C-4A57-A32A-C26F63666F18}" name="CODIGO DE LOTE" dataDxfId="37"/>
-    <tableColumn id="11" xr3:uid="{D00E48FE-8B53-44E2-A61B-9ABA1B8B7593}" name="ETAPA" dataDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{B0321528-0267-41B3-9AEC-8621E5518BF4}" name="Empresa" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{DE9E0488-4897-4D82-8726-274A71BDB0A3}" name="Temp 01 (°C)" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{39EE2A4D-7C97-4EC5-B5EC-4E60E9BB772E}" name="Temp 02 (°C)" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{5E7CEF39-CB01-4029-B90E-EFA4F1C23863}" name="Temp 03 (°C)" dataDxfId="32"/>
-    <tableColumn id="10" xr3:uid="{8966B669-DBA1-4A3A-8B9A-DD598117E7B9}" name="Promedio (°C)" dataDxfId="31">
+    <tableColumn id="1" xr3:uid="{F3C78A2A-E049-44AD-BCEF-3623D50497A2}" name="OPERADOR" dataDxfId="38"/>
+    <tableColumn id="2" xr3:uid="{A98DA936-BC9E-4B55-BBD8-F045C36ABADE}" name="Fecha  de evaluación  (dd/mm/aa)" dataDxfId="37"/>
+    <tableColumn id="6" xr3:uid="{71676037-992C-4A57-A32A-C26F63666F18}" name="CODIGO DE LOTE" dataDxfId="36"/>
+    <tableColumn id="11" xr3:uid="{D00E48FE-8B53-44E2-A61B-9ABA1B8B7593}" name="ETAPA" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{B0321528-0267-41B3-9AEC-8621E5518BF4}" name="Empresa" dataDxfId="34"/>
+    <tableColumn id="7" xr3:uid="{DE9E0488-4897-4D82-8726-274A71BDB0A3}" name="Temp 01 (°C)" dataDxfId="33"/>
+    <tableColumn id="8" xr3:uid="{39EE2A4D-7C97-4EC5-B5EC-4E60E9BB772E}" name="Temp 02 (°C)" dataDxfId="32"/>
+    <tableColumn id="9" xr3:uid="{5E7CEF39-CB01-4029-B90E-EFA4F1C23863}" name="Temp 03 (°C)" dataDxfId="31"/>
+    <tableColumn id="10" xr3:uid="{8966B669-DBA1-4A3A-8B9A-DD598117E7B9}" name="Promedio (°C)" dataDxfId="30">
       <calculatedColumnFormula>AVERAGE(Table4[[#This Row],[Temp 01 (°C)]:[Temp 03 (°C)]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{D7FA7FDE-6109-4C5D-A95A-4C51B7353232}" name="pH- 01" dataDxfId="30"/>
-    <tableColumn id="13" xr3:uid="{D50726A9-DCEC-4FA1-9733-E07D57CA8B8B}" name="pH- 02" dataDxfId="29"/>
-    <tableColumn id="14" xr3:uid="{0A9507DE-7BC9-47F6-881A-5E072A06A81A}" name="pH - 03" dataDxfId="28"/>
-    <tableColumn id="15" xr3:uid="{EF878A85-AE7F-46D1-B508-924B239399F8}" name="Promedio (pH)" dataDxfId="27">
+    <tableColumn id="12" xr3:uid="{D7FA7FDE-6109-4C5D-A95A-4C51B7353232}" name="pH- 01" dataDxfId="29"/>
+    <tableColumn id="13" xr3:uid="{D50726A9-DCEC-4FA1-9733-E07D57CA8B8B}" name="pH- 02" dataDxfId="28"/>
+    <tableColumn id="14" xr3:uid="{0A9507DE-7BC9-47F6-881A-5E072A06A81A}" name="pH - 03" dataDxfId="27"/>
+    <tableColumn id="15" xr3:uid="{EF878A85-AE7F-46D1-B508-924B239399F8}" name="Promedio (pH)" dataDxfId="26">
       <calculatedColumnFormula>AVERAGE(J2:L2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{F6B9015F-8DE0-497F-ADE2-10BDB60BA4F0}" name="Humedad (%)" dataDxfId="26"/>
-    <tableColumn id="23" xr3:uid="{BB5F943D-3345-4689-8827-3AEF1439D848}" name="N° Volteo" dataDxfId="25"/>
-    <tableColumn id="16" xr3:uid="{5894C94E-A044-49B1-A849-37637CEBD0B6}" name="Estado Humedad" dataDxfId="24">
+    <tableColumn id="18" xr3:uid="{F6B9015F-8DE0-497F-ADE2-10BDB60BA4F0}" name="Humedad (%)" dataDxfId="25"/>
+    <tableColumn id="23" xr3:uid="{BB5F943D-3345-4689-8827-3AEF1439D848}" name="N° Volteo" dataDxfId="24"/>
+    <tableColumn id="16" xr3:uid="{5894C94E-A044-49B1-A849-37637CEBD0B6}" name="Estado Humedad" dataDxfId="23">
       <calculatedColumnFormula>IF(I2&lt;_xlfn.XLOOKUP(D2,'HOJA 1. CONFIGURACION'!$C$2:$F$2,'HOJA 1. CONFIGURACION'!$C$5:$F$5),"BAJA",
 IF(I2&gt;_xlfn.XLOOKUP(D2,'HOJA 1. CONFIGURACION'!$C$2:$F$2,'HOJA 1. CONFIGURACION'!$C$6:$F$6),"ALTA",
 "CORRECTA"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{28F4C266-8129-4D1D-AC84-4A25DDDE298C}" name="Estado pH" dataDxfId="23">
+    <tableColumn id="17" xr3:uid="{28F4C266-8129-4D1D-AC84-4A25DDDE298C}" name="Estado pH" dataDxfId="22">
       <calculatedColumnFormula>IF(M2&lt;_xlfn.XLOOKUP(D2,'HOJA 1. CONFIGURACION'!$C$2:$F$2,'HOJA 1. CONFIGURACION'!$C$7:$F$7),"BAJO",
 IF(M2&gt;_xlfn.XLOOKUP(D2,'HOJA 1. CONFIGURACION'!$C$2:$F$2,'HOJA 1. CONFIGURACION'!$C$8:$F$8),"ALTO",
 "CORRECTO"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{D49ECADB-B4BE-4EE8-B866-FFA3AD6D4053}" name="Estado temperatura " dataDxfId="22">
+    <tableColumn id="5" xr3:uid="{D49ECADB-B4BE-4EE8-B866-FFA3AD6D4053}" name="Estado temperatura " dataDxfId="21">
       <calculatedColumnFormula>IF(H2&lt;_xlfn.XLOOKUP(D2,'HOJA 1. CONFIGURACION'!$C$2:$F$2,'HOJA 1. CONFIGURACION'!$C$3:$F$3),"BAJA",
 IF(H2&gt;_xlfn.XLOOKUP(D2,'HOJA 1. CONFIGURACION'!$C$2:$F$2,'HOJA 1. CONFIGURACION'!$C$4:$F$4),"ALTA",
 "CORRECTA"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{191F42DC-73FD-4EC5-A727-5414A4D292FF}" name="Estado General " dataDxfId="21">
+    <tableColumn id="4" xr3:uid="{191F42DC-73FD-4EC5-A727-5414A4D292FF}" name="Estado General " dataDxfId="20">
       <calculatedColumnFormula>IF(AND(O2="CORRECTA",P2="CORRECTA",Q2="CORRECTO"),
 "OPERACIÓN NORMAL",
 "REQUIERE AJUSTE OPERATIVO")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{ABA9E6E6-1F79-472D-9924-9383975CF038}" name="Recomendaciones " dataDxfId="20">
+    <tableColumn id="24" xr3:uid="{ABA9E6E6-1F79-472D-9924-9383975CF038}" name="Recomendaciones " dataDxfId="19">
       <calculatedColumnFormula>_xlfn.TEXTJOIN(" | ",TRUE,
 IF(P2="","",IF(P2="CORRECTA","",_xlfn.XLOOKUP("HUMEDAD|"&amp;UPPER(TRIM(CLEAN(P2))),Table8[[CLAVE ]],Table8[Recomendación],"REGLA NO ENCONTRADA"))),
 IF(Q2="","",IF(Q2="CORRECTO","",_xlfn.XLOOKUP("PH|"&amp;UPPER(TRIM(CLEAN(Q2))),Table8[[CLAVE ]],Table8[Recomendación],"REGLA NO ENCONTRADA"))),
@@ -2145,17 +2593,17 @@
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{955E1332-8DAF-4D2A-99EF-C7422B329FA3}" name="Table6" displayName="Table6" ref="A1:H12" totalsRowShown="0" headerRowDxfId="19">
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{955E1332-8DAF-4D2A-99EF-C7422B329FA3}" name="Table6" displayName="Table6" ref="A1:H12" totalsRowShown="0" headerRowDxfId="18">
   <autoFilter ref="A1:H12" xr:uid="{955E1332-8DAF-4D2A-99EF-C7422B329FA3}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{E7FE6792-8B43-4899-B52F-2627A4341A7E}" name="Fecha " dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{E7FE6792-8B43-4899-B52F-2627A4341A7E}" name="Fecha " dataDxfId="17" totalsRowDxfId="16"/>
     <tableColumn id="5" xr3:uid="{F70F8369-9120-42A9-B954-777F2A74A8A5}" name="CODIGO DE LOTE"/>
     <tableColumn id="8" xr3:uid="{77A67502-A160-469F-B38C-7C18E311DE58}" name="Numero de ficha (peso)"/>
-    <tableColumn id="2" xr3:uid="{9008020A-1342-4FFB-97C6-F89BF1A80E0E}" name="Compost ingresado a stock (ton)" dataDxfId="16" totalsRowDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{170E8184-900D-48D7-B10B-0548CCE8CEA6}" name="salida para remediacion (ton)" dataDxfId="14" totalsRowDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{F20A920A-7A51-4B06-8616-0565EDC2FE8B}" name="salida para donacion (ton)" dataDxfId="12" totalsRowDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{5984404F-2291-49B2-89BB-AB2D3AEC79CD}" name="Stock Acumulado (ton)" dataDxfId="10">
+    <tableColumn id="2" xr3:uid="{9008020A-1342-4FFB-97C6-F89BF1A80E0E}" name="Compost ingresado a stock (ton)" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{170E8184-900D-48D7-B10B-0548CCE8CEA6}" name="salida para remediacion (ton)" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{F20A920A-7A51-4B06-8616-0565EDC2FE8B}" name="salida para donacion (ton)" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{5984404F-2291-49B2-89BB-AB2D3AEC79CD}" name="Stock Acumulado (ton)" dataDxfId="9">
       <calculatedColumnFormula>IF(COUNTA(D2:F2)=0,"",G1+SUM(D2)-SUM(E2:F2))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{45696D4F-0088-4698-8EFC-8C154E2B9198}" name="Estado del inventario">
@@ -2166,8 +2614,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{D031877C-6791-43C3-9B21-0395EBF0A6F1}" name="Table7" displayName="Table7" ref="A1:F2" totalsRowShown="0" headerRowDxfId="9">
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{D031877C-6791-43C3-9B21-0395EBF0A6F1}" name="Table7" displayName="Table7" ref="A1:F2" totalsRowShown="0" headerRowDxfId="8">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{4E34FD5D-0C3F-41C7-98A8-CDD5E0E3E562}" name="Total de residuos ingresados a compostaje (ton)">
       <calculatedColumnFormula>SUM('HOJA 3. FORMULACION'!P:P)</calculatedColumnFormula>
@@ -2190,9 +2638,25 @@
 </table>
 </file>
 
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{DC0FC455-24CF-4E66-B8C2-52D6A3F8C0AC}" name="Table9" displayName="Table9" ref="A2:G11" totalsRowShown="0" dataDxfId="94">
+  <autoFilter ref="A2:G11" xr:uid="{DC0FC455-24CF-4E66-B8C2-52D6A3F8C0AC}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{CC3B574F-E27F-413D-97E8-9537DF94269A}" name="Parametro"/>
+    <tableColumn id="7" xr3:uid="{31105658-6F32-48B6-8876-D035B990630C}" name="Unidad" dataDxfId="93"/>
+    <tableColumn id="2" xr3:uid="{D682FB6B-9E90-457D-96A4-807678C3D581}" name="Mesófila I" dataDxfId="92"/>
+    <tableColumn id="3" xr3:uid="{FEA1E499-9B43-4E54-A972-9209C66C98D9}" name="Termófila " dataDxfId="91"/>
+    <tableColumn id="4" xr3:uid="{13C8682C-BAE4-4F99-BBFD-7E52F56B6430}" name="Mesófila II" dataDxfId="90"/>
+    <tableColumn id="5" xr3:uid="{843FA08B-D107-4ADF-B5AC-FD2EEDFCE796}" name="Maduración" dataDxfId="89"/>
+    <tableColumn id="6" xr3:uid="{A288719C-2759-48F8-AB04-6B0F737C89CB}" name="Fuente: " dataDxfId="88"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{C8477798-837B-4EBD-9B5E-244F15820825}" name="Table8" displayName="Table8" ref="A1:H16" insertRowShift="1" totalsRowShown="0">
-  <autoFilter ref="A1:H16" xr:uid="{C8477798-837B-4EBD-9B5E-244F15820825}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{C8477798-837B-4EBD-9B5E-244F15820825}" name="Table8" displayName="Table8" ref="A1:H19" insertRowShift="1" totalsRowShown="0">
+  <autoFilter ref="A1:H19" xr:uid="{C8477798-837B-4EBD-9B5E-244F15820825}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{58AF199E-CDFC-49F3-A3D5-C367344AC60A}" name="ID"/>
     <tableColumn id="4" xr3:uid="{F09A506E-85A0-4A6A-A7AF-59096D2E580F}" name="Modulo "/>
@@ -2201,7 +2665,7 @@
     <tableColumn id="2" xr3:uid="{4476C04B-C12D-4B84-BC3F-3D10A3C082D6}" name="Condicion "/>
     <tableColumn id="3" xr3:uid="{1E763165-1025-4880-A643-11C80DAED571}" name="RESULTADO"/>
     <tableColumn id="8" xr3:uid="{EFDB2963-3E6A-4DB0-80D9-6A8C0FA6868B}" name="Recomendación"/>
-    <tableColumn id="11" xr3:uid="{FB4556C0-23DC-4DF0-BD95-BF2D217B76D1}" name="CLAVE " dataDxfId="8">
+    <tableColumn id="11" xr3:uid="{FB4556C0-23DC-4DF0-BD95-BF2D217B76D1}" name="CLAVE " dataDxfId="95">
       <calculatedColumnFormula>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2525,373 +2989,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A8EE4C9-0208-4355-98B5-70ABA7AD9D62}">
-  <dimension ref="A1:M30"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="1" max="1" width="20.36328125" customWidth="1"/>
-    <col min="2" max="2" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.1796875" customWidth="1"/>
-    <col min="5" max="5" width="14.90625" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="18.453125" customWidth="1"/>
-    <col min="9" max="9" width="18.6328125" customWidth="1"/>
-    <col min="10" max="10" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.08984375" style="19" customWidth="1"/>
-    <col min="13" max="13" width="30.1796875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="62" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="63"/>
-      <c r="M1" s="2"/>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="M2" s="2"/>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="4">
-        <v>40</v>
-      </c>
-      <c r="D3" s="4">
-        <v>55</v>
-      </c>
-      <c r="E3" s="4">
-        <v>40</v>
-      </c>
-      <c r="F3" s="4">
-        <v>20</v>
-      </c>
-      <c r="G3" s="4"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="20"/>
-      <c r="M3" s="2"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="4">
-        <v>55</v>
-      </c>
-      <c r="D4" s="4">
-        <v>65</v>
-      </c>
-      <c r="E4" s="4">
-        <v>45</v>
-      </c>
-      <c r="F4" s="4">
-        <v>30</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I4" s="13"/>
-      <c r="J4" s="24"/>
-      <c r="M4" s="2"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C5" s="22">
-        <v>20</v>
-      </c>
-      <c r="D5" s="22">
-        <v>45</v>
-      </c>
-      <c r="E5" s="22">
-        <v>45</v>
-      </c>
-      <c r="F5" s="22">
-        <v>30</v>
-      </c>
-      <c r="G5" s="4"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="13"/>
-      <c r="M5" s="2"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="22">
-        <v>45</v>
-      </c>
-      <c r="D6" s="22">
-        <v>55</v>
-      </c>
-      <c r="E6" s="22">
-        <v>50</v>
-      </c>
-      <c r="F6" s="22">
-        <v>40</v>
-      </c>
-      <c r="G6" s="4"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="13"/>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="4">
-        <v>5.5</v>
-      </c>
-      <c r="D7" s="4">
-        <v>6</v>
-      </c>
-      <c r="E7" s="4">
-        <v>6.5</v>
-      </c>
-      <c r="F7" s="4">
-        <v>6.5</v>
-      </c>
-      <c r="G7" s="4"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="25"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" s="4">
-        <v>6.5</v>
-      </c>
-      <c r="D8" s="4">
-        <v>8.5</v>
-      </c>
-      <c r="E8" s="4">
-        <v>7.5</v>
-      </c>
-      <c r="F8" s="4">
-        <v>7</v>
-      </c>
-      <c r="G8" s="4"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="25"/>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="4">
-        <v>25</v>
-      </c>
-      <c r="D9" s="4">
-        <v>15</v>
-      </c>
-      <c r="E9" s="4">
-        <v>15</v>
-      </c>
-      <c r="F9" s="18">
-        <v>10</v>
-      </c>
-      <c r="G9" s="4"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="13"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="4">
-        <v>35</v>
-      </c>
-      <c r="D10" s="4">
-        <v>20</v>
-      </c>
-      <c r="E10" s="4">
-        <v>20</v>
-      </c>
-      <c r="F10" s="18">
-        <v>15</v>
-      </c>
-      <c r="G10" s="4"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="13"/>
-    </row>
-    <row r="11" spans="1:13" ht="43.5">
-      <c r="A11" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="F11" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="I11" s="23"/>
-      <c r="J11" s="13"/>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="I12" s="23"/>
-      <c r="J12" s="26"/>
-    </row>
-    <row r="13" spans="1:13" ht="16.5">
-      <c r="I13" s="27"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="21"/>
-    </row>
-    <row r="14" spans="1:13" ht="16.5">
-      <c r="I14" s="27"/>
-      <c r="J14" s="28"/>
-      <c r="K14" s="21"/>
-    </row>
-    <row r="15" spans="1:13" ht="16.5">
-      <c r="I15" s="27"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="21"/>
-    </row>
-    <row r="16" spans="1:13" ht="16.5">
-      <c r="I16" s="27"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="21"/>
-    </row>
-    <row r="17" spans="9:11" ht="16.5">
-      <c r="I17" s="27"/>
-      <c r="J17" s="28"/>
-      <c r="K17" s="21"/>
-    </row>
-    <row r="18" spans="9:11" ht="16.5">
-      <c r="I18" s="27"/>
-      <c r="J18" s="29"/>
-    </row>
-    <row r="19" spans="9:11" ht="16.5">
-      <c r="I19" s="27"/>
-      <c r="J19" s="28"/>
-    </row>
-    <row r="20" spans="9:11" ht="16.5">
-      <c r="I20" s="27"/>
-      <c r="J20" s="30"/>
-    </row>
-    <row r="21" spans="9:11" ht="16.5">
-      <c r="I21" s="27"/>
-      <c r="J21" s="29"/>
-    </row>
-    <row r="22" spans="9:11" ht="16.5">
-      <c r="I22" s="27"/>
-      <c r="J22" s="25"/>
-    </row>
-    <row r="23" spans="9:11" ht="16.5">
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-    </row>
-    <row r="24" spans="9:11" ht="16.5">
-      <c r="I24" s="27"/>
-      <c r="J24" s="27"/>
-    </row>
-    <row r="25" spans="9:11" ht="16.5">
-      <c r="I25" s="27"/>
-      <c r="J25" s="27"/>
-    </row>
-    <row r="26" spans="9:11" ht="16.5">
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
-    </row>
-    <row r="27" spans="9:11" ht="16.5">
-      <c r="I27" s="27"/>
-      <c r="J27" s="27"/>
-    </row>
-    <row r="28" spans="9:11" ht="16.5">
-      <c r="I28" s="27"/>
-      <c r="J28" s="27"/>
-    </row>
-    <row r="29" spans="9:11" ht="16.5">
-      <c r="I29" s="27"/>
-      <c r="J29" s="27"/>
-    </row>
-    <row r="30" spans="9:11" ht="16.5">
-      <c r="I30" s="27"/>
-      <c r="J30" s="27"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="I1:K1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E34E5C9-0647-428E-B35E-006F03DE298F}">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
@@ -3075,7 +3172,693 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC86F3E-EF03-4DBD-B46C-952999543777}">
+  <dimension ref="A1:H20"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.6328125" customWidth="1"/>
+    <col min="7" max="7" width="63.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="37.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H2" t="str">
+        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
+        <v>HUMEDAD INICIAL|BAJA</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H3" t="str">
+        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
+        <v>HUMEDAD INICIAL|ALTA</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" t="s">
+        <v>173</v>
+      </c>
+      <c r="E4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H4" t="str">
+        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
+        <v>HUMEDAD INICIAL|CORRECTA</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F5" t="s">
+        <v>114</v>
+      </c>
+      <c r="G5" t="s">
+        <v>127</v>
+      </c>
+      <c r="H5" t="str">
+        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
+        <v>RELACION C/N|BAJO</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D6" t="s">
+        <v>179</v>
+      </c>
+      <c r="E6" t="s">
+        <v>129</v>
+      </c>
+      <c r="F6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G6" t="s">
+        <v>130</v>
+      </c>
+      <c r="H6" t="str">
+        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
+        <v>RELACION C/N|ALTO</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D7" t="s">
+        <v>178</v>
+      </c>
+      <c r="E7" t="s">
+        <v>132</v>
+      </c>
+      <c r="F7" t="s">
+        <v>122</v>
+      </c>
+      <c r="G7" t="s">
+        <v>133</v>
+      </c>
+      <c r="H7" t="str">
+        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
+        <v>RELACION C/N|CORRECTO</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>160</v>
+      </c>
+      <c r="B8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D8" t="s">
+        <v>170</v>
+      </c>
+      <c r="E8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H8" t="str">
+        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
+        <v>TEMPERATURA|BAJA</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D9" t="s">
+        <v>171</v>
+      </c>
+      <c r="E9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F9" t="s">
+        <v>114</v>
+      </c>
+      <c r="G9" t="s">
+        <v>155</v>
+      </c>
+      <c r="H9" t="str">
+        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
+        <v>TEMPERATURA|ALTA</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>162</v>
+      </c>
+      <c r="B10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" t="s">
+        <v>173</v>
+      </c>
+      <c r="E10" t="s">
+        <v>143</v>
+      </c>
+      <c r="F10" t="s">
+        <v>122</v>
+      </c>
+      <c r="G10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H10" t="str">
+        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
+        <v>TEMPERATURA|CORRECTA</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>163</v>
+      </c>
+      <c r="B11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D11" t="s">
+        <v>177</v>
+      </c>
+      <c r="E11" t="s">
+        <v>146</v>
+      </c>
+      <c r="F11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G11" t="s">
+        <v>156</v>
+      </c>
+      <c r="H11" t="str">
+        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
+        <v>PH|BAJO</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>164</v>
+      </c>
+      <c r="B12" t="s">
+        <v>139</v>
+      </c>
+      <c r="C12" t="s">
+        <v>145</v>
+      </c>
+      <c r="D12" t="s">
+        <v>179</v>
+      </c>
+      <c r="E12" t="s">
+        <v>151</v>
+      </c>
+      <c r="F12" t="s">
+        <v>114</v>
+      </c>
+      <c r="G12" t="s">
+        <v>157</v>
+      </c>
+      <c r="H12" t="str">
+        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
+        <v>PH|ALTO</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>165</v>
+      </c>
+      <c r="B13" t="s">
+        <v>139</v>
+      </c>
+      <c r="C13" t="s">
+        <v>145</v>
+      </c>
+      <c r="D13" t="s">
+        <v>178</v>
+      </c>
+      <c r="E13" t="s">
+        <v>169</v>
+      </c>
+      <c r="F13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G13" t="s">
+        <v>158</v>
+      </c>
+      <c r="H13" t="str">
+        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
+        <v>PH|CORRECTO</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>166</v>
+      </c>
+      <c r="B14" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" t="s">
+        <v>147</v>
+      </c>
+      <c r="D14" t="s">
+        <v>170</v>
+      </c>
+      <c r="E14" t="s">
+        <v>149</v>
+      </c>
+      <c r="F14" t="s">
+        <v>114</v>
+      </c>
+      <c r="G14" t="s">
+        <v>153</v>
+      </c>
+      <c r="H14" t="str">
+        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
+        <v>HUMEDAD|BAJA</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>167</v>
+      </c>
+      <c r="B15" t="s">
+        <v>139</v>
+      </c>
+      <c r="C15" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" t="s">
+        <v>171</v>
+      </c>
+      <c r="E15" t="s">
+        <v>150</v>
+      </c>
+      <c r="F15" t="s">
+        <v>114</v>
+      </c>
+      <c r="G15" t="s">
+        <v>152</v>
+      </c>
+      <c r="H15" t="str">
+        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
+        <v>HUMEDAD|ALTA</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>168</v>
+      </c>
+      <c r="B16" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" t="s">
+        <v>148</v>
+      </c>
+      <c r="D16" t="s">
+        <v>173</v>
+      </c>
+      <c r="E16" t="s">
+        <v>121</v>
+      </c>
+      <c r="F16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G16" t="s">
+        <v>154</v>
+      </c>
+      <c r="H16" t="str">
+        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
+        <v>HUMEDAD|CORRECTA</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="29">
+      <c r="A17" t="s">
+        <v>235</v>
+      </c>
+      <c r="B17" s="52" t="s">
+        <v>234</v>
+      </c>
+      <c r="C17" s="70" t="s">
+        <v>240</v>
+      </c>
+      <c r="D17" s="70" t="s">
+        <v>246</v>
+      </c>
+      <c r="E17" s="80" t="s">
+        <v>239</v>
+      </c>
+      <c r="F17" t="s">
+        <v>122</v>
+      </c>
+      <c r="G17" s="35" t="s">
+        <v>238</v>
+      </c>
+      <c r="H17" t="str">
+        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
+        <v>ESTADO DE CAPACIDAD|ADMISIBLE</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="29">
+      <c r="A18" t="s">
+        <v>236</v>
+      </c>
+      <c r="B18" s="52" t="s">
+        <v>234</v>
+      </c>
+      <c r="C18" s="70" t="s">
+        <v>240</v>
+      </c>
+      <c r="D18" s="70" t="s">
+        <v>247</v>
+      </c>
+      <c r="E18" s="80" t="s">
+        <v>241</v>
+      </c>
+      <c r="F18" t="s">
+        <v>242</v>
+      </c>
+      <c r="G18" s="35" t="s">
+        <v>243</v>
+      </c>
+      <c r="H18" t="str">
+        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
+        <v>ESTADO DE CAPACIDAD|ADMISIBLE CON AJUSTE DE HUMEDAD</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="43.5">
+      <c r="A19" t="s">
+        <v>237</v>
+      </c>
+      <c r="B19" s="52" t="s">
+        <v>234</v>
+      </c>
+      <c r="C19" s="70" t="s">
+        <v>240</v>
+      </c>
+      <c r="D19" s="70" t="s">
+        <v>248</v>
+      </c>
+      <c r="E19" s="81" t="s">
+        <v>244</v>
+      </c>
+      <c r="F19" t="s">
+        <v>114</v>
+      </c>
+      <c r="G19" s="35" t="s">
+        <v>245</v>
+      </c>
+      <c r="H19" t="str">
+        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
+        <v>ESTADO DE CAPACIDAD|NO ADMISIBLE</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="82"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E00855F-9B54-46BB-9A9B-78CAC456D492}">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="32.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="45.36328125" customWidth="1"/>
+    <col min="10" max="10" width="45.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="105" t="s">
+        <v>254</v>
+      </c>
+      <c r="B1" s="105" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1" s="105" t="s">
+        <v>255</v>
+      </c>
+      <c r="D1" s="105" t="s">
+        <v>256</v>
+      </c>
+      <c r="E1" s="105" t="s">
+        <v>257</v>
+      </c>
+      <c r="F1" s="105" t="s">
+        <v>258</v>
+      </c>
+      <c r="G1" s="105" t="s">
+        <v>259</v>
+      </c>
+      <c r="H1" s="105" t="s">
+        <v>260</v>
+      </c>
+      <c r="I1" s="105" t="s">
+        <v>277</v>
+      </c>
+      <c r="J1" s="105" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="29">
+      <c r="A2" s="104">
+        <v>1</v>
+      </c>
+      <c r="B2" s="102" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" s="102" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2" s="102" t="s">
+        <v>268</v>
+      </c>
+      <c r="E2" s="102" t="s">
+        <v>273</v>
+      </c>
+      <c r="F2" s="102" t="s">
+        <v>273</v>
+      </c>
+      <c r="G2" s="102" t="s">
+        <v>274</v>
+      </c>
+      <c r="H2" s="101" t="s">
+        <v>261</v>
+      </c>
+      <c r="I2" s="103" t="s">
+        <v>238</v>
+      </c>
+      <c r="J2" s="103" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="43.5">
+      <c r="A3" s="104">
+        <v>2</v>
+      </c>
+      <c r="B3" s="102" t="s">
+        <v>263</v>
+      </c>
+      <c r="C3" s="102" t="s">
+        <v>266</v>
+      </c>
+      <c r="D3" s="102" t="s">
+        <v>269</v>
+      </c>
+      <c r="E3" s="102" t="s">
+        <v>272</v>
+      </c>
+      <c r="F3" s="102" t="s">
+        <v>272</v>
+      </c>
+      <c r="G3" s="102" t="s">
+        <v>274</v>
+      </c>
+      <c r="H3" s="102" t="s">
+        <v>275</v>
+      </c>
+      <c r="I3" s="103" t="s">
+        <v>243</v>
+      </c>
+      <c r="J3" s="103" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="43.5">
+      <c r="A4" s="104">
+        <v>3</v>
+      </c>
+      <c r="B4" s="102" t="s">
+        <v>264</v>
+      </c>
+      <c r="C4" s="102" t="s">
+        <v>267</v>
+      </c>
+      <c r="D4" s="102" t="s">
+        <v>270</v>
+      </c>
+      <c r="E4" s="102" t="s">
+        <v>271</v>
+      </c>
+      <c r="F4" s="102" t="s">
+        <v>271</v>
+      </c>
+      <c r="G4" s="102" t="s">
+        <v>274</v>
+      </c>
+      <c r="H4" s="102" t="s">
+        <v>276</v>
+      </c>
+      <c r="I4" s="103" t="s">
+        <v>245</v>
+      </c>
+      <c r="J4" s="103" t="s">
+        <v>245</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A7ED473-6CB4-473B-B54C-0E5339BF8A5A}">
   <dimension ref="A1:W23"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -3106,32 +3889,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="18.5">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="73" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
       <c r="I1" s="46"/>
       <c r="J1" s="46"/>
       <c r="K1" s="46"/>
-      <c r="L1" s="65" t="s">
+      <c r="L1" s="74" t="s">
         <v>106</v>
       </c>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="61" t="s">
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="75" t="s">
         <v>105</v>
       </c>
-      <c r="R1" s="61"/>
-      <c r="S1" s="61"/>
-      <c r="T1" s="61"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="75"/>
     </row>
     <row r="2" spans="1:23" ht="43.5">
       <c r="A2" s="1" t="s">
@@ -3281,13 +4064,13 @@
 IF(S3="ALTO",
 "Incrementar material con mayor aporte de nitrógeno.",
 "Revisar la formulación."))))))))))</f>
-        <v>La formulación cumple los criterios iniciales para conformar la pila.</v>
+        <v>Ajustar la humedad inicial antes de conformar la pila.</v>
       </c>
       <c r="R3" s="42" t="str">
         <f>IF(L3&lt;'HOJA 1. CONFIGURACION'!$C$5,"BAJA",
 IF(L3&gt;'HOJA 1. CONFIGURACION'!$C$6,"ALTA",
 "CORRECTA"))</f>
-        <v>CORRECTA</v>
+        <v>BAJA</v>
       </c>
       <c r="S3" s="42" t="str">
         <f>IF(O3&lt;'HOJA 1. CONFIGURACION'!$C$9,"BAJO",
@@ -3297,11 +4080,11 @@
       </c>
       <c r="T3" s="54" t="str">
         <f t="shared" ref="T3:T8" si="2">IF(OR(R3="",S3=""),"",IF(AND(TRIM(R3)="CORRECTA",TRIM(S3)="CORRECTO"),"APROBADA","REFORMULAR"))</f>
-        <v>APROBADA</v>
+        <v>REFORMULAR</v>
       </c>
       <c r="U3" s="51" t="str">
         <f>IF(R3="","",IF(R3="CORRECTA","",_xlfn.XLOOKUP("Humedad inicial|"&amp;TRIM(R3),Table8[[CLAVE ]],Table8[Recomendación],"REGLA NO ENCONTRADA")))</f>
-        <v/>
+        <v xml:space="preserve">Incrementar la humedad inicial de la mezcla antes de conformar la pila </v>
       </c>
       <c r="V3" s="52" t="str">
         <f>IF(S3="","",IF(S3="CORRECTO","",_xlfn.XLOOKUP("Relacion C/N|"&amp;TRIM(S3),Table8[[CLAVE ]],Table8[Recomendación],"REGLA NO ENCONTRADA")))</f>
@@ -3309,7 +4092,7 @@
       </c>
       <c r="W3" s="35" t="str">
         <f t="shared" ref="W3:W6" si="3">IF(T3="","",IF(T3="APROBADA","La formulación cumple los parámetros establecidos para iniciar el compostaje.",_xlfn.TEXTJOIN(" | ",TRUE,U3,V3)))</f>
-        <v>La formulación cumple los parámetros establecidos para iniciar el compostaje.</v>
+        <v xml:space="preserve">Incrementar la humedad inicial de la mezcla antes de conformar la pila </v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="29">
@@ -3370,13 +4153,13 @@
       </c>
       <c r="Q4" t="str">
         <f t="shared" si="1"/>
-        <v>La formulación cumple los criterios iniciales para conformar la pila.</v>
+        <v>Ajustar la humedad inicial antes de conformar la pila.</v>
       </c>
       <c r="R4" s="42" t="str">
         <f>IF(L4&lt;'HOJA 1. CONFIGURACION'!$C$5,"BAJA",
 IF(L4&gt;'HOJA 1. CONFIGURACION'!$C$6,"ALTA",
 "CORRECTA"))</f>
-        <v>CORRECTA</v>
+        <v>BAJA</v>
       </c>
       <c r="S4" s="42" t="str">
         <f>IF(O4&lt;'HOJA 1. CONFIGURACION'!$C$9,"BAJO",
@@ -3386,11 +4169,11 @@
       </c>
       <c r="T4" s="54" t="str">
         <f t="shared" si="2"/>
-        <v>APROBADA</v>
+        <v>REFORMULAR</v>
       </c>
       <c r="U4" s="51" t="str">
         <f>IF(R4="","",IF(R4="CORRECTA","",_xlfn.XLOOKUP("Humedad inicial|"&amp;TRIM(R4),Table8[[CLAVE ]],Table8[Recomendación],"REGLA NO ENCONTRADA")))</f>
-        <v/>
+        <v xml:space="preserve">Incrementar la humedad inicial de la mezcla antes de conformar la pila </v>
       </c>
       <c r="V4" s="4" t="str">
         <f>IF(S4="","",IF(S4="CORRECTO","",_xlfn.XLOOKUP("Relacion C/N|"&amp;TRIM(S4),Table8[[CLAVE ]],Table8[Recomendación],"REGLA NO ENCONTRADA")))</f>
@@ -3398,7 +4181,7 @@
       </c>
       <c r="W4" s="35" t="str">
         <f t="shared" si="3"/>
-        <v>La formulación cumple los parámetros establecidos para iniciar el compostaje.</v>
+        <v xml:space="preserve">Incrementar la humedad inicial de la mezcla antes de conformar la pila </v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="29">
@@ -3456,13 +4239,13 @@
       </c>
       <c r="Q5" t="str">
         <f t="shared" si="1"/>
-        <v>Incrementar material rico en carbono, como cartón.</v>
+        <v>Ajustar la humedad e incrementar material rico en carbono antes de conformar la pila.</v>
       </c>
       <c r="R5" s="42" t="str">
         <f>IF(L5&lt;'HOJA 1. CONFIGURACION'!$C$5,"BAJA",
 IF(L5&gt;'HOJA 1. CONFIGURACION'!$C$6,"ALTA",
 "CORRECTA"))</f>
-        <v>CORRECTA</v>
+        <v>BAJA</v>
       </c>
       <c r="S5" s="42" t="str">
         <f>IF(O5&lt;'HOJA 1. CONFIGURACION'!$C$9,"BAJO",
@@ -3476,7 +4259,7 @@
       </c>
       <c r="U5" s="51" t="str">
         <f>IF(R5="","",IF(R5="CORRECTA","",_xlfn.XLOOKUP("Humedad inicial|"&amp;TRIM(R5),Table8[[CLAVE ]],Table8[Recomendación],"REGLA NO ENCONTRADA")))</f>
-        <v/>
+        <v xml:space="preserve">Incrementar la humedad inicial de la mezcla antes de conformar la pila </v>
       </c>
       <c r="V5" s="4" t="str">
         <f>IF(S5="","",IF(S5="CORRECTO","",_xlfn.XLOOKUP("Relacion C/N|"&amp;TRIM(S5),Table8[[CLAVE ]],Table8[Recomendación],"REGLA NO ENCONTRADA")))</f>
@@ -3484,7 +4267,7 @@
       </c>
       <c r="W5" s="35" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">Incrementar materiales ricos en carbono, como aserrin, podas, etc </v>
+        <v xml:space="preserve">Incrementar la humedad inicial de la mezcla antes de conformar la pila  | Incrementar materiales ricos en carbono, como aserrin, podas, etc </v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="29">
@@ -3536,13 +4319,13 @@
       </c>
       <c r="Q6" t="str">
         <f t="shared" si="1"/>
-        <v>La formulación cumple los criterios iniciales para conformar la pila.</v>
+        <v>Ajustar la humedad inicial antes de conformar la pila.</v>
       </c>
       <c r="R6" s="42" t="str">
         <f>IF(L6&lt;'HOJA 1. CONFIGURACION'!$C$5,"BAJA",
 IF(L6&gt;'HOJA 1. CONFIGURACION'!$C$6,"ALTA",
 "CORRECTA"))</f>
-        <v>CORRECTA</v>
+        <v>BAJA</v>
       </c>
       <c r="S6" s="42" t="str">
         <f>IF(O6&lt;'HOJA 1. CONFIGURACION'!$C$9,"BAJO",
@@ -3552,11 +4335,11 @@
       </c>
       <c r="T6" s="54" t="str">
         <f t="shared" si="2"/>
-        <v>APROBADA</v>
+        <v>REFORMULAR</v>
       </c>
       <c r="U6" s="51" t="str">
         <f>IF(R6="","",IF(R6="CORRECTA","",_xlfn.XLOOKUP("Humedad inicial|"&amp;TRIM(R6),Table8[[CLAVE ]],Table8[Recomendación],"REGLA NO ENCONTRADA")))</f>
-        <v/>
+        <v xml:space="preserve">Incrementar la humedad inicial de la mezcla antes de conformar la pila </v>
       </c>
       <c r="V6" s="4" t="str">
         <f>IF(S6="","",IF(S6="CORRECTO","",_xlfn.XLOOKUP("Relacion C/N|"&amp;TRIM(S6),Table8[[CLAVE ]],Table8[Recomendación],"REGLA NO ENCONTRADA")))</f>
@@ -3564,7 +4347,7 @@
       </c>
       <c r="W6" s="35" t="str">
         <f t="shared" si="3"/>
-        <v>La formulación cumple los parámetros establecidos para iniciar el compostaje.</v>
+        <v xml:space="preserve">Incrementar la humedad inicial de la mezcla antes de conformar la pila </v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="29">
@@ -3641,13 +4424,13 @@
 IF(S7="ALTO",
 "Incrementar material con mayor aporte de nitrógeno.",
 "Revisar la formulación."))))))))))</f>
-        <v>La formulación cumple los criterios iniciales para conformar la pila.</v>
+        <v>Ajustar la humedad inicial antes de conformar la pila.</v>
       </c>
       <c r="R7" s="42" t="str">
         <f>IF(L7&lt;'HOJA 1. CONFIGURACION'!$C$5,"BAJA",
 IF(L7&gt;'HOJA 1. CONFIGURACION'!$C$6,"ALTA",
 "CORRECTA"))</f>
-        <v>CORRECTA</v>
+        <v>BAJA</v>
       </c>
       <c r="S7" s="42" t="str">
         <f>IF(O7&lt;'HOJA 1. CONFIGURACION'!$C$9,"BAJO",
@@ -3657,11 +4440,11 @@
       </c>
       <c r="T7" s="54" t="str">
         <f t="shared" si="2"/>
-        <v>APROBADA</v>
+        <v>REFORMULAR</v>
       </c>
       <c r="U7" s="51" t="str">
         <f>IF(R7="","",IF(R7="CORRECTA","",_xlfn.XLOOKUP("Humedad inicial|"&amp;TRIM(R7),Table8[[CLAVE ]],Table8[Recomendación],"REGLA NO ENCONTRADA")))</f>
-        <v/>
+        <v xml:space="preserve">Incrementar la humedad inicial de la mezcla antes de conformar la pila </v>
       </c>
       <c r="V7" s="4" t="str">
         <f>IF(S7="","",IF(S7="CORRECTO","",_xlfn.XLOOKUP("Relacion C/N|"&amp;TRIM(S7),Table8[[CLAVE ]],Table8[Recomendación],"REGLA NO ENCONTRADA")))</f>
@@ -3669,7 +4452,7 @@
       </c>
       <c r="W7" s="35" t="str">
         <f>IF(T7="","",IF(T7="APROBADA","La formulación cumple los parámetros establecidos para iniciar el compostaje.",_xlfn.TEXTJOIN(" | ",TRUE,U7,V7)))</f>
-        <v>La formulación cumple los parámetros establecidos para iniciar el compostaje.</v>
+        <v xml:space="preserve">Incrementar la humedad inicial de la mezcla antes de conformar la pila </v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="43.5">
@@ -3829,7 +4612,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42F91974-E493-40FF-8C17-618957632CE7}">
   <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -4051,17 +4834,17 @@
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="B8" s="67" t="s">
+      <c r="B8" s="77" t="s">
         <v>176</v>
       </c>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="66"/>
+      <c r="C9" s="76"/>
       <c r="D9" s="8">
         <f>IFERROR(I6/B6*100,0)</f>
         <v>32.5</v>
@@ -4069,30 +4852,30 @@
       <c r="E9" s="38"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="B10" s="66" t="s">
+      <c r="B10" s="76" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="66"/>
+      <c r="C10" s="76"/>
       <c r="D10" s="8">
         <f>IFERROR(F6/D6*100,0)</f>
         <v>45.025925925925932</v>
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="B11" s="66" t="s">
+      <c r="B11" s="76" t="s">
         <v>103</v>
       </c>
-      <c r="C11" s="66"/>
+      <c r="C11" s="76"/>
       <c r="D11" s="8">
         <f>IFERROR(H6/D6*100,0)</f>
         <v>1.3274074074074074</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="B12" s="66" t="s">
+      <c r="B12" s="76" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="66"/>
+      <c r="C12" s="76"/>
       <c r="D12" s="8">
         <f>IFERROR(F6/H6,0)</f>
         <v>33.920200892857146</v>
@@ -4113,7 +4896,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A852DB0F-8808-45FA-82FF-80BFB093FCA2}">
   <dimension ref="A1:P8"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -4137,30 +4920,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18.5">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="75" t="s">
         <v>213</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="59" t="s">
+      <c r="B1" s="75"/>
+      <c r="C1" s="78" t="s">
         <v>210</v>
       </c>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="60" t="s">
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="61" t="s">
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="75" t="s">
         <v>212</v>
       </c>
-      <c r="N1" s="61"/>
-      <c r="O1" s="61"/>
-      <c r="P1" s="61"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+      <c r="P1" s="75"/>
     </row>
     <row r="2" spans="1:16" s="49" customFormat="1" ht="39">
       <c r="A2" s="48" t="s">
@@ -4694,7 +5477,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26852189-2CF0-43C9-BF4D-ADDC1083F29A}">
   <dimension ref="A1:T5"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -4829,7 +5612,7 @@
         <f>IF(I2&lt;_xlfn.XLOOKUP(D2,'HOJA 1. CONFIGURACION'!$C$2:$F$2,'HOJA 1. CONFIGURACION'!$C$5:$F$5),"BAJA",
 IF(I2&gt;_xlfn.XLOOKUP(D2,'HOJA 1. CONFIGURACION'!$C$2:$F$2,'HOJA 1. CONFIGURACION'!$C$6:$F$6),"ALTA",
 "CORRECTA"))</f>
-        <v>CORRECTA</v>
+        <v>BAJA</v>
       </c>
       <c r="Q2" s="1" t="str">
         <f>IF(M2&lt;_xlfn.XLOOKUP(D2,'HOJA 1. CONFIGURACION'!$C$2:$F$2,'HOJA 1. CONFIGURACION'!$C$7:$F$7),"BAJO",
@@ -4855,7 +5638,7 @@
 IF(Q2="","",IF(Q2="CORRECTO","",_xlfn.XLOOKUP("PH|"&amp;UPPER(TRIM(CLEAN(Q2))),Table8[[CLAVE ]],Table8[Recomendación],"REGLA NO ENCONTRADA"))),
 IF(R2="","",IF(R2="CORRECTA","",_xlfn.XLOOKUP("TEMPERATURA|"&amp;UPPER(TRIM(CLEAN(R2))),Table8[[CLAVE ]],Table8[Recomendación],"REGLA NO ENCONTRADA")))
 )</f>
-        <v>Revisar composición de la mezcla y continuar el seguimiento del pH.</v>
+        <v>Adicionar agua durante el volteo hasta alcanzar el rango recomendado. | Revisar composición de la mezcla y continuar el seguimiento del pH.</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -4878,7 +5661,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{436ED903-F5E2-4B10-BBD1-5934259DE560}">
   <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -5109,7 +5892,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ADC0449-B9FF-4E66-AA8A-176294E5A959}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -5172,453 +5955,577 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC86F3E-EF03-4DBD-B46C-952999543777}">
-  <dimension ref="A1:H16"/>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D6B0CA9-885E-4DD1-AF08-A2DC0DFB8176}">
+  <dimension ref="A2:D23"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.6328125" customWidth="1"/>
-    <col min="7" max="7" width="63.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="37.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.6328125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="39.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.90625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.36328125" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="2" spans="1:4" ht="29">
+      <c r="A2" s="69" t="s">
+        <v>216</v>
+      </c>
+      <c r="B2" s="83">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="43.5">
+      <c r="A3" s="69" t="s">
+        <v>217</v>
+      </c>
+      <c r="B3" s="83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="43.5">
+      <c r="A4" s="69" t="s">
+        <v>218</v>
+      </c>
+      <c r="B4" s="83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="18.5">
+      <c r="A5" s="59" t="s">
+        <v>250</v>
+      </c>
+      <c r="B5" s="65">
+        <f>'HOJA 1. CONFIGURACION'!$C$9</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="18.5">
+      <c r="A6" s="89" t="s">
+        <v>249</v>
+      </c>
+      <c r="B6" s="90">
+        <f>'HOJA 1. CONFIGURACION'!$C$10</f>
         <v>35</v>
       </c>
-      <c r="D1" t="s">
-        <v>174</v>
-      </c>
-      <c r="E1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" t="s">
-        <v>172</v>
-      </c>
-      <c r="G1" t="s">
-        <v>113</v>
-      </c>
-      <c r="H1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+    </row>
+    <row r="7" spans="1:4" ht="29">
+      <c r="A7" s="89" t="s">
+        <v>252</v>
+      </c>
+      <c r="B7" s="88">
+        <f>'HOJA 1. CONFIGURACION'!$C$5</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="29">
+      <c r="A8" s="89" t="s">
+        <v>251</v>
+      </c>
+      <c r="B8" s="91">
+        <f>'HOJA 1. CONFIGURACION'!$C$6</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="29">
+      <c r="A9" s="60" t="s">
+        <v>219</v>
+      </c>
+      <c r="B9" s="85">
+        <f>B2*(1-'HOJA 2. INSUMOS'!$C$2/100)*'HOJA 2. INSUMOS'!$D$2/100
++B3*(1-'HOJA 2. INSUMOS'!$C$5/100)*'HOJA 2. INSUMOS'!$D$5/100
++B4*(1-'HOJA 2. INSUMOS'!$C$4/100)*'HOJA 2. INSUMOS'!$D$4/100</f>
+        <v>0.19199999999999995</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="29">
+      <c r="A10" s="61" t="s">
+        <v>220</v>
+      </c>
+      <c r="B10" s="85">
+        <f>B2*(1-'HOJA 2. INSUMOS'!$C$2/100)*'HOJA 2. INSUMOS'!$E$2/100
++B3*(1-'HOJA 2. INSUMOS'!$C$5/100)*'HOJA 2. INSUMOS'!$E$5/100
++B4*(1-'HOJA 2. INSUMOS'!$C$4/100)*'HOJA 2. INSUMOS'!$E$4/100</f>
+        <v>1.2799999999999999E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="43.5">
+      <c r="A11" s="62" t="s">
+        <v>221</v>
+      </c>
+      <c r="B11" s="86">
+        <f>(1-'HOJA 2. INSUMOS'!$C$3/100)*'HOJA 2. INSUMOS'!$D$3/100</f>
+        <v>0.192</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="43.5">
+      <c r="A12" s="66" t="s">
+        <v>222</v>
+      </c>
+      <c r="B12" s="85">
+        <f>(1-'HOJA 2. INSUMOS'!$C$3/100)*'HOJA 2. INSUMOS'!$E$3/100</f>
+        <v>2.1000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="42">
+      <c r="A13" s="95" t="s">
+        <v>223</v>
+      </c>
+      <c r="B13" s="96">
+        <f>IFERROR(MAX(0,(B9-B5*B10)/(B5*B12-B11)),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="29">
+      <c r="A14" s="67" t="s">
+        <v>224</v>
+      </c>
+      <c r="B14" s="84">
+        <f>B2*'HOJA 2. INSUMOS'!$C$2/100+B3*'HOJA 2. INSUMOS'!$C$5/100+B4*'HOJA 2. INSUMOS'!$C$4/100</f>
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="18.5">
+      <c r="A15" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="B15" s="84">
+        <f>SUM(B2:B4)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="29">
+      <c r="A16" s="67" t="s">
+        <v>226</v>
+      </c>
+      <c r="B16" s="64" t="str">
+        <f>IF('HOJA 2. INSUMOS'!$C$3/100&lt;=$B$8,"NO LIMITA",MAX(0,($B$8*B15-B14)/('HOJA 2. INSUMOS'!$C$3/100-$B$8)))</f>
+        <v>NO LIMITA</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="63">
+      <c r="A17" s="99" t="s">
+        <v>228</v>
+      </c>
+      <c r="B17" s="100">
+        <f>IF(B16="NO LIMITA",B13,MIN(B13,B16))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="29">
+      <c r="A18" s="63" t="s">
+        <v>229</v>
+      </c>
+      <c r="B18" s="87">
+        <f>B15+B17</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="63">
+      <c r="A19" s="96" t="s">
+        <v>230</v>
+      </c>
+      <c r="B19" s="97">
+        <f>(B14+B17*'HOJA 2. INSUMOS'!$C$3/100)/B18</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="42">
+      <c r="A20" s="96" t="s">
+        <v>231</v>
+      </c>
+      <c r="B20" s="94">
+        <f>IFERROR((B9+B17*B11)/(B10+B17*B12),0)</f>
+        <v>14.999999999999996</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="98" t="s">
+        <v>232</v>
+      </c>
+      <c r="B22" s="92" t="str">
+        <f>IF(OR(B20&lt;B5,B20&gt;B6,B19&gt;B8/100),"NO ADMISIBLE",IF(B19&lt;B7/100,"ADMISIBLE CON AJUSTE DE HUMEDAD","ADMISIBLE"))</f>
+        <v>NO ADMISIBLE</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="64">
+      <c r="A23" s="98" t="s">
+        <v>233</v>
+      </c>
+      <c r="B23" s="93" t="str">
+        <f>_xlfn.XLOOKUP("ESTADO DE CAPACIDAD|"&amp;UPPER(TRIM(CLEAN(B22))),Table8[[CLAVE ]],Table8[Recomendación],"REGLA NO ENCONTRADA")</f>
+        <v xml:space="preserve">La cantidad de lodo propuesta no cumple los criterios establecidos. Ajustar la cantidad de lodo y/o la composicion de la mezcla antes de conformar la pila. </v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A8EE4C9-0208-4355-98B5-70ABA7AD9D62}">
+  <dimension ref="A1:M30"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="20.36328125" customWidth="1"/>
+    <col min="2" max="2" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1796875" customWidth="1"/>
+    <col min="5" max="5" width="14.90625" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="18.453125" customWidth="1"/>
+    <col min="9" max="9" width="18.6328125" customWidth="1"/>
+    <col min="10" max="10" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.08984375" style="19" customWidth="1"/>
+    <col min="13" max="13" width="30.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="71" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="M1" s="2"/>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>116</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>170</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="F2" t="s">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="G2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H2" t="str">
-        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
-        <v>HUMEDAD INICIAL|BAJA</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>44</v>
+      </c>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="M2" s="2"/>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F3" t="s">
-        <v>114</v>
-      </c>
-      <c r="G3" t="s">
-        <v>119</v>
-      </c>
-      <c r="H3" t="str">
-        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
-        <v>HUMEDAD INICIAL|ALTA</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>36</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="4">
+        <v>40</v>
+      </c>
+      <c r="D3" s="4">
+        <v>55</v>
+      </c>
+      <c r="E3" s="4">
+        <v>40</v>
+      </c>
+      <c r="F3" s="4">
+        <v>20</v>
+      </c>
+      <c r="G3" s="4"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="20"/>
+      <c r="M3" s="2"/>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D4" t="s">
-        <v>173</v>
-      </c>
-      <c r="E4" t="s">
-        <v>121</v>
-      </c>
-      <c r="F4" t="s">
-        <v>122</v>
-      </c>
-      <c r="G4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H4" t="str">
-        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
-        <v>HUMEDAD INICIAL|CORRECTA</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>43</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="4">
+        <v>55</v>
+      </c>
+      <c r="D4" s="4">
+        <v>65</v>
+      </c>
+      <c r="E4" s="4">
+        <v>45</v>
+      </c>
+      <c r="F4" s="4">
+        <v>30</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I4" s="13"/>
+      <c r="J4" s="24"/>
+      <c r="M4" s="2"/>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E5" t="s">
-        <v>126</v>
-      </c>
-      <c r="F5" t="s">
-        <v>114</v>
-      </c>
-      <c r="G5" t="s">
-        <v>127</v>
-      </c>
-      <c r="H5" t="str">
-        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
-        <v>RELACION C/N|BAJO</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>37</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="22">
+        <v>50</v>
+      </c>
+      <c r="D5" s="22">
+        <v>45</v>
+      </c>
+      <c r="E5" s="22">
+        <v>45</v>
+      </c>
+      <c r="F5" s="22">
+        <v>30</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="13"/>
+      <c r="M5" s="2"/>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>128</v>
-      </c>
-      <c r="B6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C6" t="s">
-        <v>125</v>
-      </c>
-      <c r="D6" t="s">
-        <v>179</v>
-      </c>
-      <c r="E6" t="s">
-        <v>129</v>
-      </c>
-      <c r="F6" t="s">
-        <v>114</v>
-      </c>
-      <c r="G6" t="s">
-        <v>130</v>
-      </c>
-      <c r="H6" t="str">
-        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
-        <v>RELACION C/N|ALTO</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="22">
+        <v>60</v>
+      </c>
+      <c r="D6" s="22">
+        <v>55</v>
+      </c>
+      <c r="E6" s="22">
+        <v>50</v>
+      </c>
+      <c r="F6" s="22">
+        <v>40</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="13"/>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>131</v>
-      </c>
-      <c r="B7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C7" t="s">
-        <v>125</v>
-      </c>
-      <c r="D7" t="s">
-        <v>178</v>
-      </c>
-      <c r="E7" t="s">
-        <v>132</v>
-      </c>
-      <c r="F7" t="s">
-        <v>122</v>
-      </c>
-      <c r="G7" t="s">
-        <v>133</v>
-      </c>
-      <c r="H7" t="str">
-        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
-        <v>RELACION C/N|CORRECTO</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>39</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="D7" s="4">
+        <v>6</v>
+      </c>
+      <c r="E7" s="4">
+        <v>6.5</v>
+      </c>
+      <c r="F7" s="4">
+        <v>6.5</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="25"/>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>160</v>
-      </c>
-      <c r="B8" t="s">
-        <v>139</v>
-      </c>
-      <c r="C8" t="s">
-        <v>140</v>
-      </c>
-      <c r="D8" t="s">
-        <v>170</v>
-      </c>
-      <c r="E8" t="s">
-        <v>141</v>
-      </c>
-      <c r="F8" t="s">
-        <v>114</v>
-      </c>
-      <c r="G8" t="s">
-        <v>144</v>
-      </c>
-      <c r="H8" t="str">
-        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
-        <v>TEMPERATURA|BAJA</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>42</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="4">
+        <v>6.5</v>
+      </c>
+      <c r="D8" s="4">
+        <v>8.5</v>
+      </c>
+      <c r="E8" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="F8" s="4">
+        <v>7</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="25"/>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>161</v>
-      </c>
-      <c r="B9" t="s">
-        <v>139</v>
-      </c>
-      <c r="C9" t="s">
-        <v>140</v>
-      </c>
-      <c r="D9" t="s">
-        <v>171</v>
-      </c>
-      <c r="E9" t="s">
-        <v>142</v>
-      </c>
-      <c r="F9" t="s">
-        <v>114</v>
-      </c>
-      <c r="G9" t="s">
-        <v>155</v>
-      </c>
-      <c r="H9" t="str">
-        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
-        <v>TEMPERATURA|ALTA</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>40</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="4">
+        <v>25</v>
+      </c>
+      <c r="D9" s="4">
+        <v>15</v>
+      </c>
+      <c r="E9" s="4">
+        <v>15</v>
+      </c>
+      <c r="F9" s="18">
+        <v>10</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="13"/>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>162</v>
-      </c>
-      <c r="B10" t="s">
-        <v>139</v>
-      </c>
-      <c r="C10" t="s">
-        <v>140</v>
-      </c>
-      <c r="D10" t="s">
-        <v>173</v>
-      </c>
-      <c r="E10" t="s">
-        <v>143</v>
-      </c>
-      <c r="F10" t="s">
-        <v>122</v>
-      </c>
-      <c r="G10" t="s">
-        <v>159</v>
-      </c>
-      <c r="H10" t="str">
-        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
-        <v>TEMPERATURA|CORRECTA</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>163</v>
-      </c>
-      <c r="B11" t="s">
-        <v>139</v>
-      </c>
-      <c r="C11" t="s">
-        <v>145</v>
-      </c>
-      <c r="D11" t="s">
-        <v>177</v>
-      </c>
-      <c r="E11" t="s">
-        <v>146</v>
-      </c>
-      <c r="F11" t="s">
-        <v>114</v>
-      </c>
-      <c r="G11" t="s">
-        <v>156</v>
-      </c>
-      <c r="H11" t="str">
-        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
-        <v>PH|BAJO</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
-        <v>164</v>
-      </c>
-      <c r="B12" t="s">
-        <v>139</v>
-      </c>
-      <c r="C12" t="s">
-        <v>145</v>
-      </c>
-      <c r="D12" t="s">
-        <v>179</v>
-      </c>
-      <c r="E12" t="s">
-        <v>151</v>
-      </c>
-      <c r="F12" t="s">
-        <v>114</v>
-      </c>
-      <c r="G12" t="s">
-        <v>157</v>
-      </c>
-      <c r="H12" t="str">
-        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
-        <v>PH|ALTO</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
-        <v>165</v>
-      </c>
-      <c r="B13" t="s">
-        <v>139</v>
-      </c>
-      <c r="C13" t="s">
-        <v>145</v>
-      </c>
-      <c r="D13" t="s">
-        <v>178</v>
-      </c>
-      <c r="E13" t="s">
-        <v>169</v>
-      </c>
-      <c r="F13" t="s">
-        <v>122</v>
-      </c>
-      <c r="G13" t="s">
-        <v>158</v>
-      </c>
-      <c r="H13" t="str">
-        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
-        <v>PH|CORRECTO</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" t="s">
-        <v>166</v>
-      </c>
-      <c r="B14" t="s">
-        <v>139</v>
-      </c>
-      <c r="C14" t="s">
-        <v>147</v>
-      </c>
-      <c r="D14" t="s">
-        <v>170</v>
-      </c>
-      <c r="E14" t="s">
-        <v>149</v>
-      </c>
-      <c r="F14" t="s">
-        <v>114</v>
-      </c>
-      <c r="G14" t="s">
-        <v>153</v>
-      </c>
-      <c r="H14" t="str">
-        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
-        <v>HUMEDAD|BAJA</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" t="s">
-        <v>167</v>
-      </c>
-      <c r="B15" t="s">
-        <v>139</v>
-      </c>
-      <c r="C15" t="s">
-        <v>148</v>
-      </c>
-      <c r="D15" t="s">
-        <v>171</v>
-      </c>
-      <c r="E15" t="s">
-        <v>150</v>
-      </c>
-      <c r="F15" t="s">
-        <v>114</v>
-      </c>
-      <c r="G15" t="s">
-        <v>152</v>
-      </c>
-      <c r="H15" t="str">
-        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
-        <v>HUMEDAD|ALTA</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" t="s">
-        <v>168</v>
-      </c>
-      <c r="B16" t="s">
-        <v>139</v>
-      </c>
-      <c r="C16" t="s">
-        <v>148</v>
-      </c>
-      <c r="D16" t="s">
-        <v>173</v>
-      </c>
-      <c r="E16" t="s">
-        <v>121</v>
-      </c>
-      <c r="F16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G16" t="s">
-        <v>154</v>
-      </c>
-      <c r="H16" t="str">
-        <f>UPPER(TRIM(CLEAN(Table8[[#This Row],[Parametro]])))&amp;"|"&amp;UPPER(TRIM(CLEAN(Table8[[#This Row],[ESTADO EVALUADO]])))</f>
-        <v>HUMEDAD|CORRECTA</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="4">
+        <v>35</v>
+      </c>
+      <c r="D10" s="4">
+        <v>20</v>
+      </c>
+      <c r="E10" s="4">
+        <v>20</v>
+      </c>
+      <c r="F10" s="18">
+        <v>15</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="13"/>
+    </row>
+    <row r="11" spans="1:13" ht="43.5">
+      <c r="A11" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11" s="23"/>
+      <c r="J11" s="13"/>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="I12" s="23"/>
+      <c r="J12" s="26"/>
+    </row>
+    <row r="13" spans="1:13" ht="16.5">
+      <c r="I13" s="27"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="21"/>
+    </row>
+    <row r="14" spans="1:13" ht="16.5">
+      <c r="I14" s="27"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="21"/>
+    </row>
+    <row r="15" spans="1:13" ht="16.5">
+      <c r="I15" s="27"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="21"/>
+    </row>
+    <row r="16" spans="1:13" ht="16.5">
+      <c r="I16" s="27"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="21"/>
+    </row>
+    <row r="17" spans="9:11" ht="16.5">
+      <c r="I17" s="27"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="21"/>
+    </row>
+    <row r="18" spans="9:11" ht="16.5">
+      <c r="I18" s="27"/>
+      <c r="J18" s="29"/>
+    </row>
+    <row r="19" spans="9:11" ht="16.5">
+      <c r="I19" s="27"/>
+      <c r="J19" s="28"/>
+    </row>
+    <row r="20" spans="9:11" ht="16.5">
+      <c r="I20" s="27"/>
+      <c r="J20" s="30"/>
+    </row>
+    <row r="21" spans="9:11" ht="16.5">
+      <c r="I21" s="27"/>
+      <c r="J21" s="29"/>
+    </row>
+    <row r="22" spans="9:11" ht="16.5">
+      <c r="I22" s="27"/>
+      <c r="J22" s="25"/>
+    </row>
+    <row r="23" spans="9:11" ht="16.5">
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+    </row>
+    <row r="24" spans="9:11" ht="16.5">
+      <c r="I24" s="27"/>
+      <c r="J24" s="27"/>
+    </row>
+    <row r="25" spans="9:11" ht="16.5">
+      <c r="I25" s="27"/>
+      <c r="J25" s="27"/>
+    </row>
+    <row r="26" spans="9:11" ht="16.5">
+      <c r="I26" s="27"/>
+      <c r="J26" s="27"/>
+    </row>
+    <row r="27" spans="9:11" ht="16.5">
+      <c r="I27" s="27"/>
+      <c r="J27" s="27"/>
+    </row>
+    <row r="28" spans="9:11" ht="16.5">
+      <c r="I28" s="27"/>
+      <c r="J28" s="27"/>
+    </row>
+    <row r="29" spans="9:11" ht="16.5">
+      <c r="I29" s="27"/>
+      <c r="J29" s="27"/>
+    </row>
+    <row r="30" spans="9:11" ht="16.5">
+      <c r="I30" s="27"/>
+      <c r="J30" s="27"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="I1:K1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
